--- a/Luban/Datas/Player.xlsx
+++ b/Luban/Datas/Player.xlsx
@@ -2366,7 +2366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
@@ -2610,7 +2610,7 @@
         <v>-0.08</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>43</v>
+        <v>308</v>
       </c>
       <c r="S4" s="1">
         <v>0.16</v>

--- a/Luban/Datas/Player.xlsx
+++ b/Luban/Datas/Player.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="1" r:id="R264c7c84ac7744d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Background" sheetId="2" r:id="R1e156cd3da914964"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="3" r:id="R39d6e1fa800a46e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="4" r:id="Radccf8949c36495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyDrop" sheetId="5" r:id="Rd734b86c3acf48d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="6" r:id="R764600422b804175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet" sheetId="7" r:id="R54fa242120944f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missile" sheetId="8" r:id="R20b8cf9aba764aed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulletPattern" sheetId="9" r:id="Rd14eb1753402441f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MissilePattern" sheetId="10" r:id="R326d5184ac3b43e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="11" r:id="R1b431dcabab44c1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="12" r:id="Re3d2c63b29824d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageEvent" sheetId="13" r:id="R74bfbdc35b664ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhase" sheetId="14" r:id="R9db49fe6c99a4d2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhasePattern" sheetId="15" r:id="Rd94b31f4fda644ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkill" sheetId="16" r:id="Rb7ee2e8167aa4642"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="1" r:id="Rcf773640a2c24865"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Background" sheetId="2" r:id="Rae8478ec65a54de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="3" r:id="R33c652e18c504c11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="4" r:id="R1fbd18504eaf4387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyDrop" sheetId="5" r:id="R08ad0edb8c234028"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="6" r:id="R2c3ba4e12bf04d19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet" sheetId="7" r:id="R02e08701001d4839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missile" sheetId="8" r:id="Rea74f44b946a4be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulletPattern" sheetId="9" r:id="Rb180fa12d6934398"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MissilePattern" sheetId="10" r:id="R0eed5206ddaa4379"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="11" r:id="Rc3f9abaa1af94590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="12" r:id="R8f8a2c397bc64d2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageEvent" sheetId="13" r:id="Rf39d8cbb7a354e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhase" sheetId="14" r:id="R928abaec565941b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhasePattern" sheetId="15" r:id="R4d0e629b9a0c4110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkill" sheetId="16" r:id="R45f19327949748bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2339,6 +2339,7 @@
     <x:col min="16" max="17" width="16.33203125" customWidth="1"/>
     <x:col min="18" max="18" width="18.33203125" customWidth="1"/>
     <x:col min="19" max="19" width="15.33203125" customWidth="1"/>
+    <x:col min="20" max="20" width="48.88999938964844" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2582,7 +2583,7 @@
         <x:v>0.16</x:v>
       </x:c>
       <x:c r="T4" t="str">
-        <x:v>Assets/Art/Sound/player01.wav</x:v>
+        <x:v>Assets/Art/Sound/SFX/Player/SFX_Player_Shoot_Normal_01.wav</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Luban/Datas/Player.xlsx
+++ b/Luban/Datas/Player.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="1" r:id="Rcf773640a2c24865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Background" sheetId="2" r:id="Rae8478ec65a54de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="3" r:id="R33c652e18c504c11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="4" r:id="R1fbd18504eaf4387"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyDrop" sheetId="5" r:id="R08ad0edb8c234028"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="6" r:id="R2c3ba4e12bf04d19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet" sheetId="7" r:id="R02e08701001d4839"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missile" sheetId="8" r:id="Rea74f44b946a4be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulletPattern" sheetId="9" r:id="Rb180fa12d6934398"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MissilePattern" sheetId="10" r:id="R0eed5206ddaa4379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="11" r:id="Rc3f9abaa1af94590"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="12" r:id="R8f8a2c397bc64d2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageEvent" sheetId="13" r:id="Rf39d8cbb7a354e1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhase" sheetId="14" r:id="R928abaec565941b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhasePattern" sheetId="15" r:id="R4d0e629b9a0c4110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkill" sheetId="16" r:id="R45f19327949748bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="1" r:id="Rea182594321246dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Background" sheetId="2" r:id="R778a1a71f83b4b1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="3" r:id="Ra429881ee4fa4f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="4" r:id="R1aa01ac3c4454650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyDrop" sheetId="5" r:id="R4dad2eeb4efc4944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="6" r:id="R86096c344bb94c24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet" sheetId="7" r:id="Red895ee02cc1463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missile" sheetId="8" r:id="R31c468d20ff14466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulletPattern" sheetId="9" r:id="Rf5aace0add8b4e7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MissilePattern" sheetId="10" r:id="Rfaf526ab267a4375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="11" r:id="R4ec2db3432ee4c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="12" r:id="R138068ff803f4171"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageEvent" sheetId="13" r:id="R9e97058ad23545aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhase" sheetId="14" r:id="R8e8618a6a98b4074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPhasePattern" sheetId="15" r:id="R25ae457ad356426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkill" sheetId="16" r:id="R668f5c259d964006"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -149,9 +149,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">warplane_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Warplane 01</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Assets/Prefabs/Player/warplane-01.prefab</x:t>
@@ -2534,11 +2531,11 @@
       <x:c r="C4" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="D4" s="1" t="str">
+        <x:v>雷霆战机 01</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>3</x:v>
@@ -2577,7 +2574,7 @@
         <x:v>-0.08</x:v>
       </x:c>
       <x:c r="R4" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="S4" s="1">
         <x:v>0.16</x:v>
@@ -2622,49 +2619,49 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="F1" s="2" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>433</x:v>
-      </x:c>
       <x:c r="I1" s="2" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>435</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="M1" s="2" t="s">
         <x:v>479</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
-        <x:v>480</x:v>
-      </x:c>
       <x:c r="N1" s="2" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="O1" s="2" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="s">
+      <x:c r="P1" s="2" t="s">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="s">
+      <x:c r="Q1" s="2" t="s">
         <x:v>440</x:v>
-      </x:c>
-      <x:c r="Q1" s="2" t="s">
-        <x:v>441</x:v>
       </x:c>
       <x:c r="R1" s="2" t="s">
         <x:v>18</x:v>
@@ -2711,13 +2708,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="O2" s="3" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="s">
         <x:v>20</x:v>
@@ -2731,70 +2728,70 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>481</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="H3" s="4" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="I3" s="4" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="J3" s="4" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="K3" s="4" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="L3" s="4" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="F3" s="4" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="H3" s="4" t="s">
-        <x:v>447</x:v>
-      </x:c>
-      <x:c r="I3" s="4" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="J3" s="4" t="s">
-        <x:v>449</x:v>
-      </x:c>
-      <x:c r="K3" s="4" t="s">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L3" s="4" t="s">
-        <x:v>483</x:v>
-      </x:c>
       <x:c r="M3" s="4" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="N3" s="4" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="N3" s="4" t="s">
+      <x:c r="O3" s="4" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="O3" s="4" t="s">
+      <x:c r="P3" s="4" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="P3" s="4" t="s">
+      <x:c r="Q3" s="4" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="Q3" s="4" t="s">
+      <x:c r="R3" s="4" t="s">
         <x:v>456</x:v>
-      </x:c>
-      <x:c r="R3" s="4" t="s">
-        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>0</x:v>
@@ -2839,16 +2836,16 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>0</x:v>
@@ -2893,16 +2890,16 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>0</x:v>
@@ -2947,16 +2944,16 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>0</x:v>
@@ -3001,16 +2998,16 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>0</x:v>
@@ -3055,16 +3052,16 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>0</x:v>
@@ -3109,16 +3106,16 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>0</x:v>
@@ -3163,16 +3160,16 @@
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>491</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>492</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>0</x:v>
@@ -3217,16 +3214,16 @@
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>493</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>494</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>0</x:v>
@@ -3271,16 +3268,16 @@
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>495</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>402</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>496</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>0</x:v>
@@ -3325,16 +3322,16 @@
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>497</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>402</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>498</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>0</x:v>
@@ -3379,16 +3376,16 @@
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>499</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>500</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>0</x:v>
@@ -3433,16 +3430,16 @@
     <x:row r="16">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>501</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>502</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>0</x:v>
@@ -3487,16 +3484,16 @@
     <x:row r="17">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
         <x:v>503</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>504</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>0</x:v>
@@ -3541,16 +3538,16 @@
     <x:row r="18">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
         <x:v>505</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>506</x:v>
       </x:c>
       <x:c r="F18" s="1">
         <x:v>0</x:v>
@@ -3615,10 +3612,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
         <x:v>507</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>508</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3640,19 +3637,19 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>509</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>510</x:v>
-      </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>511</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1">
@@ -3662,7 +3659,7 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1">
@@ -3672,7 +3669,7 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="C6" s="1"/>
       <x:c r="D6" s="1">
@@ -3682,7 +3679,7 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="C7" s="1"/>
       <x:c r="D7" s="1">
@@ -3692,7 +3689,7 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="C8" s="1"/>
       <x:c r="D8" s="1">
@@ -3702,7 +3699,7 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="C9" s="1"/>
       <x:c r="D9" s="1">
@@ -3712,7 +3709,7 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>518</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="C10" s="1"/>
       <x:c r="D10" s="1">
@@ -3722,7 +3719,7 @@
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="C11" s="1"/>
       <x:c r="D11" s="1">
@@ -3732,7 +3729,7 @@
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="C12" s="1"/>
       <x:c r="D12" s="1">
@@ -3742,7 +3739,7 @@
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C13" s="1"/>
       <x:c r="D13" s="1">
@@ -3752,7 +3749,7 @@
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C14" s="1"/>
       <x:c r="D14" s="1">
@@ -3762,7 +3759,7 @@
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="C15" s="1"/>
       <x:c r="D15" s="1">
@@ -3772,7 +3769,7 @@
     <x:row r="16">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="C16" s="1"/>
       <x:c r="D16" s="1">
@@ -3782,7 +3779,7 @@
     <x:row r="17">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="C17" s="1"/>
       <x:c r="D17" s="1">
@@ -3822,43 +3819,43 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
         <x:v>526</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>527</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>528</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>529</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
         <x:v>530</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
+      <x:c r="L1" s="2" t="s">
         <x:v>531</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="M1" s="2" t="s">
         <x:v>532</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
+      <x:c r="N1" s="2" t="s">
         <x:v>533</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="O1" s="2" t="s">
         <x:v>534</x:v>
-      </x:c>
-      <x:c r="O1" s="2" t="s">
-        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3896,7 +3893,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
         <x:v>22</x:v>
@@ -3913,61 +3910,61 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>536</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>537</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
+      <x:c r="E3" s="4" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="s">
+      <x:c r="F3" s="4" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="s">
+      <x:c r="H3" s="4" t="s">
         <x:v>540</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="s">
+      <x:c r="I3" s="4" t="s">
         <x:v>541</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="s">
+      <x:c r="J3" s="4" t="s">
         <x:v>542</x:v>
       </x:c>
-      <x:c r="J3" s="4" t="s">
+      <x:c r="K3" s="4" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="K3" s="4" t="s">
+      <x:c r="L3" s="4" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="L3" s="4" t="s">
+      <x:c r="M3" s="4" t="s">
         <x:v>545</x:v>
       </x:c>
-      <x:c r="M3" s="4" t="s">
+      <x:c r="N3" s="4" t="s">
         <x:v>546</x:v>
       </x:c>
-      <x:c r="N3" s="4" t="s">
+      <x:c r="O3" s="4" t="s">
         <x:v>547</x:v>
-      </x:c>
-      <x:c r="O3" s="4" t="s">
-        <x:v>548</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>549</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>3</x:v>
@@ -3982,10 +3979,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K4" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="L4" s="5" t="b">
         <x:v>0</x:v>
@@ -4003,16 +4000,16 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>551</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>4</x:v>
@@ -4027,10 +4024,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K5" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="L5" s="5" t="b">
         <x:v>0</x:v>
@@ -4048,16 +4045,16 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>552</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -4072,10 +4069,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K6" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="L6" s="5" t="b">
         <x:v>0</x:v>
@@ -4093,16 +4090,16 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>554</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>6</x:v>
@@ -4117,10 +4114,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K7" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="L7" s="5" t="b">
         <x:v>0</x:v>
@@ -4138,16 +4135,16 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>3</x:v>
@@ -4162,10 +4159,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K8" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="L8" s="5" t="b">
         <x:v>0</x:v>
@@ -4183,16 +4180,16 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>557</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>2</x:v>
@@ -4207,10 +4204,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="L9" s="5" t="b">
         <x:v>0</x:v>
@@ -4228,16 +4225,16 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>558</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>5</x:v>
@@ -4252,10 +4249,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>559</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="L10" s="5" t="b">
         <x:v>0</x:v>
@@ -4273,16 +4270,16 @@
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
-        <x:v>560</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>4</x:v>
@@ -4297,10 +4294,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K11" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="L11" s="5" t="b">
         <x:v>0</x:v>
@@ -4318,16 +4315,16 @@
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>518</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>3</x:v>
@@ -4342,10 +4339,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="K12" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="L12" s="5" t="b">
         <x:v>0</x:v>
@@ -4363,16 +4360,16 @@
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
-        <x:v>563</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>8</x:v>
@@ -4387,10 +4384,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K13" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="L13" s="5" t="b">
         <x:v>0</x:v>
@@ -4408,16 +4405,16 @@
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
-        <x:v>564</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>3</x:v>
@@ -4432,10 +4429,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K14" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="L14" s="5" t="b">
         <x:v>0</x:v>
@@ -4453,16 +4450,16 @@
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>1</x:v>
@@ -4477,10 +4474,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="L15" s="5" t="b">
         <x:v>0</x:v>
@@ -4498,16 +4495,16 @@
     <x:row r="16">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="s">
-        <x:v>566</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>6</x:v>
@@ -4522,10 +4519,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K16" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="L16" s="5" t="b">
         <x:v>0</x:v>
@@ -4543,16 +4540,16 @@
     <x:row r="17">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1" t="s">
-        <x:v>567</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>5</x:v>
@@ -4567,10 +4564,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K17" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="L17" s="5" t="b">
         <x:v>0</x:v>
@@ -4588,16 +4585,16 @@
     <x:row r="18">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1" t="s">
-        <x:v>568</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F18" s="1">
         <x:v>2</x:v>
@@ -4612,10 +4609,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="K18" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="L18" s="5" t="b">
         <x:v>0</x:v>
@@ -4633,16 +4630,16 @@
     <x:row r="19">
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1" t="s">
-        <x:v>569</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>4</x:v>
@@ -4657,10 +4654,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K19" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="L19" s="5" t="b">
         <x:v>0</x:v>
@@ -4678,16 +4675,16 @@
     <x:row r="20">
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1" t="s">
-        <x:v>570</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F20" s="1">
         <x:v>2</x:v>
@@ -4702,10 +4699,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K20" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="L20" s="5" t="b">
         <x:v>0</x:v>
@@ -4723,16 +4720,16 @@
     <x:row r="21">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="1" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F21" s="1">
         <x:v>6</x:v>
@@ -4747,10 +4744,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K21" s="1" t="s">
-        <x:v>559</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="L21" s="5" t="b">
         <x:v>0</x:v>
@@ -4768,16 +4765,16 @@
     <x:row r="22">
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F22" s="1">
         <x:v>4</x:v>
@@ -4792,10 +4789,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="K22" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="L22" s="5" t="b">
         <x:v>0</x:v>
@@ -4813,16 +4810,16 @@
     <x:row r="23">
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="1" t="s">
-        <x:v>573</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F23" s="1">
         <x:v>5</x:v>
@@ -4837,10 +4834,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K23" s="1" t="s">
-        <x:v>559</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="L23" s="5" t="b">
         <x:v>0</x:v>
@@ -4858,16 +4855,16 @@
     <x:row r="24">
       <x:c r="A24" s="1"/>
       <x:c r="B24" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F24" s="1">
         <x:v>1</x:v>
@@ -4883,7 +4880,7 @@
       </x:c>
       <x:c r="J24" s="1"/>
       <x:c r="K24" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="L24" s="5" t="b">
         <x:v>1</x:v>
@@ -4923,16 +4920,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
         <x:v>507</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>508</x:v>
-      </x:c>
       <x:c r="E1" s="2" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
         <x:v>576</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>577</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -4952,7 +4949,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28">
@@ -4960,32 +4957,32 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="s">
         <x:v>578</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="D3" s="4" t="s">
+      <x:c r="E3" s="4" t="s">
         <x:v>579</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="s">
+      <x:c r="F3" s="4" t="s">
         <x:v>580</x:v>
-      </x:c>
-      <x:c r="F3" s="4" t="s">
-        <x:v>581</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>582</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>583</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F4" s="5" t="b">
         <x:v>0</x:v>
@@ -4994,14 +4991,14 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>584</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>585</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="F5" s="5" t="b">
         <x:v>0</x:v>
@@ -5010,14 +5007,14 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>586</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="C6" s="1"/>
       <x:c r="D6" s="1">
         <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>587</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="F6" s="5" t="b">
         <x:v>0</x:v>
@@ -5026,14 +5023,14 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>588</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="C7" s="1"/>
       <x:c r="D7" s="1">
         <x:v>150</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="F7" s="5" t="b">
         <x:v>1</x:v>
@@ -5042,14 +5039,14 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="C8" s="1"/>
       <x:c r="D8" s="1">
         <x:v>165</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="F8" s="5" t="b">
         <x:v>1</x:v>
@@ -5058,14 +5055,14 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>592</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="C9" s="1"/>
       <x:c r="D9" s="1">
         <x:v>176</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="F9" s="5" t="b">
         <x:v>1</x:v>
@@ -5074,14 +5071,14 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>594</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="C10" s="1"/>
       <x:c r="D10" s="1">
         <x:v>178</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>595</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F10" s="5" t="b">
         <x:v>1</x:v>
@@ -5117,31 +5114,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
         <x:v>596</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>597</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>598</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
         <x:v>599</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5184,31 +5181,31 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>601</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>602</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
+      <x:c r="E3" s="4" t="s">
         <x:v>603</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="s">
+      <x:c r="F3" s="4" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="s">
         <x:v>604</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="s">
+      <x:c r="H3" s="4" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="I3" s="4" t="s">
         <x:v>605</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="s">
-        <x:v>457</x:v>
-      </x:c>
-      <x:c r="I3" s="4" t="s">
+      <x:c r="J3" s="4" t="s">
         <x:v>606</x:v>
-      </x:c>
-      <x:c r="J3" s="4" t="s">
-        <x:v>607</x:v>
       </x:c>
       <x:c r="K3" s="4" t="s">
         <x:v>31</x:v>
@@ -5217,13 +5214,13 @@
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>608</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>609</x:v>
       </x:c>
       <x:c r="E4" s="1">
         <x:v>1</x:v>
@@ -5250,13 +5247,13 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>610</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>611</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>0.66</x:v>
@@ -5283,13 +5280,13 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>612</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>613</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>0.33</x:v>
@@ -5316,13 +5313,13 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>614</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>615</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>1</x:v>
@@ -5349,13 +5346,13 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>616</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>617</x:v>
       </x:c>
       <x:c r="E8" s="1">
         <x:v>1</x:v>
@@ -5382,13 +5379,13 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>618</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>619</x:v>
       </x:c>
       <x:c r="E9" s="1">
         <x:v>1</x:v>
@@ -5415,13 +5412,13 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>620</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>621</x:v>
       </x:c>
       <x:c r="E10" s="1">
         <x:v>1</x:v>
@@ -5448,13 +5445,13 @@
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>622</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>623</x:v>
       </x:c>
       <x:c r="E11" s="1">
         <x:v>1</x:v>
@@ -5481,13 +5478,13 @@
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>624</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>625</x:v>
       </x:c>
       <x:c r="E12" s="1">
         <x:v>1</x:v>
@@ -5535,13 +5532,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
         <x:v>626</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>627</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5566,571 +5563,571 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>628</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>629</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
+      <x:c r="E3" s="4" t="s">
         <x:v>630</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>632</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>608</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>462</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>608</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>464</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>466</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
-        <x:v>640</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
-        <x:v>643</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="s">
-        <x:v>644</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>614</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1" t="s">
-        <x:v>645</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>614</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>614</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1" t="s">
-        <x:v>647</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>616</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>616</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="1" t="s">
-        <x:v>649</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>616</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="1" t="s">
-        <x:v>650</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>616</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>494</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>618</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="1"/>
       <x:c r="B24" s="1" t="s">
-        <x:v>652</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>618</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="1"/>
       <x:c r="B25" s="1" t="s">
-        <x:v>653</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>618</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="1" t="s">
-        <x:v>654</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>618</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="1"/>
       <x:c r="B27" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="1"/>
       <x:c r="B28" s="1" t="s">
-        <x:v>656</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="1"/>
       <x:c r="B29" s="1" t="s">
-        <x:v>657</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="1" t="s">
-        <x:v>658</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>502</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1" t="s">
-        <x:v>659</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="1"/>
       <x:c r="B32" s="1" t="s">
-        <x:v>660</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="1"/>
       <x:c r="B33" s="1" t="s">
-        <x:v>661</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>494</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="1" t="s">
-        <x:v>662</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1" t="s">
-        <x:v>663</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>502</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="1" t="s">
-        <x:v>664</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="1"/>
       <x:c r="B37" s="1" t="s">
-        <x:v>665</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="1"/>
       <x:c r="B38" s="1" t="s">
-        <x:v>666</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>496</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="1"/>
       <x:c r="B39" s="1" t="s">
-        <x:v>667</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1" t="s">
-        <x:v>668</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>504</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6159,22 +6156,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>596</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>669</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>434</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6208,37 +6205,37 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
         <x:v>670</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>604</x:v>
-      </x:c>
-      <x:c r="F3" s="4" t="s">
-        <x:v>671</x:v>
-      </x:c>
       <x:c r="G3" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H3" s="4" t="s">
-        <x:v>450</x:v>
+        <x:v>449</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E4" s="1">
         <x:v>1</x:v>
@@ -6256,13 +6253,13 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>673</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>0.55000000000000004</x:v>
@@ -6300,10 +6297,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6325,22 +6322,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>2.1</x:v>
@@ -6372,7 +6369,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6394,157 +6391,157 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
+      <x:c r="D8" s="1" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>91</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6589,19 +6586,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6633,7 +6630,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
         <x:v>20</x:v>
@@ -6644,46 +6641,46 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C3" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D3" s="4" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="F3" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="G3" s="4" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H3" s="4" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="s">
+      <x:c r="I3" s="4" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="s">
+      <x:c r="J3" s="4" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="J3" s="4" t="s">
+      <x:c r="K3" s="4" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="K3" s="4" t="s">
-        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="E4" s="1">
         <x:v>3</x:v>
@@ -6695,10 +6692,10 @@
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="I4" s="1" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="I4" s="1" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="J4" s="5" t="b">
         <x:v>0</x:v>
@@ -6710,13 +6707,13 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>8</x:v>
@@ -6728,10 +6725,10 @@
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J5" s="5" t="b">
         <x:v>0</x:v>
@@ -6743,13 +6740,13 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>115</x:v>
-      </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>5</x:v>
@@ -6761,10 +6758,10 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="I6" s="1" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="J6" s="5" t="b">
         <x:v>0</x:v>
@@ -6776,13 +6773,13 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>4</x:v>
@@ -6794,10 +6791,10 @@
         <x:v>1.1000000000000001</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J7" s="5" t="b">
         <x:v>0</x:v>
@@ -6809,13 +6806,13 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E8" s="1">
         <x:v>10</x:v>
@@ -6827,10 +6824,10 @@
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="J8" s="5" t="b">
         <x:v>0</x:v>
@@ -6842,13 +6839,13 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="E9" s="1">
         <x:v>160</x:v>
@@ -6860,7 +6857,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I9" s="1"/>
       <x:c r="J9" s="5" t="b">
@@ -6873,13 +6870,13 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="E10" s="1">
         <x:v>172</x:v>
@@ -6891,7 +6888,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I10" s="1"/>
       <x:c r="J10" s="5" t="b">
@@ -6904,13 +6901,13 @@
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="E11" s="1">
         <x:v>184</x:v>
@@ -6922,7 +6919,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I11" s="1"/>
       <x:c r="J11" s="5" t="b">
@@ -6935,13 +6932,13 @@
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="E12" s="1">
         <x:v>196</x:v>
@@ -6953,7 +6950,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I12" s="1"/>
       <x:c r="J12" s="5" t="b">
@@ -6966,13 +6963,13 @@
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="E13" s="1">
         <x:v>208</x:v>
@@ -6984,7 +6981,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I13" s="1"/>
       <x:c r="J13" s="5" t="b">
@@ -6997,13 +6994,13 @@
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="E14" s="1">
         <x:v>220</x:v>
@@ -7015,7 +7012,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I14" s="1"/>
       <x:c r="J14" s="5" t="b">
@@ -7028,13 +7025,13 @@
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="E15" s="1">
         <x:v>232</x:v>
@@ -7046,7 +7043,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I15" s="1"/>
       <x:c r="J15" s="5" t="b">
@@ -7059,13 +7056,13 @@
     <x:row r="16">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="E16" s="1">
         <x:v>244</x:v>
@@ -7077,7 +7074,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I16" s="1"/>
       <x:c r="J16" s="5" t="b">
@@ -7090,13 +7087,13 @@
     <x:row r="17">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="E17" s="1">
         <x:v>256</x:v>
@@ -7108,7 +7105,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I17" s="1"/>
       <x:c r="J17" s="5" t="b">
@@ -7121,13 +7118,13 @@
     <x:row r="18">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="E18" s="1">
         <x:v>268</x:v>
@@ -7139,7 +7136,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I18" s="1"/>
       <x:c r="J18" s="5" t="b">
@@ -7152,13 +7149,13 @@
     <x:row r="19">
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="E19" s="1">
         <x:v>280</x:v>
@@ -7170,7 +7167,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I19" s="1"/>
       <x:c r="J19" s="5" t="b">
@@ -7183,13 +7180,13 @@
     <x:row r="20">
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="E20" s="1">
         <x:v>292</x:v>
@@ -7201,7 +7198,7 @@
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I20" s="1"/>
       <x:c r="J20" s="5" t="b">
@@ -7214,13 +7211,13 @@
     <x:row r="21">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="D21" s="1" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="E21" s="1">
         <x:v>95</x:v>
@@ -7232,7 +7229,7 @@
         <x:v>1.28</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I21" s="1"/>
       <x:c r="J21" s="5" t="b">
@@ -7245,13 +7242,13 @@
     <x:row r="22">
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
+      <x:c r="D22" s="1" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="E22" s="1">
         <x:v>125</x:v>
@@ -7263,7 +7260,7 @@
         <x:v>1.21</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I22" s="1"/>
       <x:c r="J22" s="5" t="b">
@@ -7276,13 +7273,13 @@
     <x:row r="23">
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>156</x:v>
       </x:c>
       <x:c r="E23" s="1">
         <x:v>155</x:v>
@@ -7294,7 +7291,7 @@
         <x:v>1.1400000000000001</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I23" s="1"/>
       <x:c r="J23" s="5" t="b">
@@ -7307,13 +7304,13 @@
     <x:row r="24">
       <x:c r="A24" s="1"/>
       <x:c r="B24" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24" s="1" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="E24" s="1">
         <x:v>185</x:v>
@@ -7325,7 +7322,7 @@
         <x:v>1.07</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I24" s="1"/>
       <x:c r="J24" s="5" t="b">
@@ -7338,13 +7335,13 @@
     <x:row r="25">
       <x:c r="A25" s="1"/>
       <x:c r="B25" s="1" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
+      <x:c r="D25" s="1" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="E25" s="1">
         <x:v>230</x:v>
@@ -7356,7 +7353,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I25" s="1"/>
       <x:c r="J25" s="5" t="b">
@@ -7369,13 +7366,13 @@
     <x:row r="26">
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="E26" s="1">
         <x:v>290</x:v>
@@ -7387,7 +7384,7 @@
         <x:v>0.92999999999999994</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I26" s="1"/>
       <x:c r="J26" s="5" t="b">
@@ -7421,19 +7418,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="E1" s="2" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="F1" s="2" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -7456,7 +7453,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -7464,37 +7461,37 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
+      <x:c r="E3" s="4" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="s">
+      <x:c r="F3" s="4" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="s">
+      <x:c r="G3" s="4" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="s">
-        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D4" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D4" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>178</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>1</x:v>
@@ -7506,16 +7503,16 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>1</x:v>
@@ -7527,16 +7524,16 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>1</x:v>
@@ -7548,16 +7545,16 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>2</x:v>
@@ -7569,16 +7566,16 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>2</x:v>
@@ -7590,16 +7587,16 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>1</x:v>
@@ -7611,16 +7608,16 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>1</x:v>
@@ -7632,16 +7629,16 @@
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>2</x:v>
@@ -7653,10 +7650,10 @@
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>3</x:v>
@@ -7674,16 +7671,16 @@
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>1</x:v>
@@ -7695,16 +7692,16 @@
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>1</x:v>
@@ -7716,10 +7713,10 @@
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>3</x:v>
@@ -7737,16 +7734,16 @@
     <x:row r="16">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>3</x:v>
@@ -7758,16 +7755,16 @@
     <x:row r="17">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>3</x:v>
@@ -7779,16 +7776,16 @@
     <x:row r="18">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F18" s="1">
         <x:v>20</x:v>
@@ -7800,16 +7797,16 @@
     <x:row r="19">
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>20</x:v>
@@ -7821,16 +7818,16 @@
     <x:row r="20">
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F20" s="1">
         <x:v>20</x:v>
@@ -7842,16 +7839,16 @@
     <x:row r="21">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F21" s="1">
         <x:v>20</x:v>
@@ -7863,16 +7860,16 @@
     <x:row r="22">
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F22" s="1">
         <x:v>20</x:v>
@@ -7884,16 +7881,16 @@
     <x:row r="23">
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F23" s="1">
         <x:v>20</x:v>
@@ -7905,16 +7902,16 @@
     <x:row r="24">
       <x:c r="A24" s="1"/>
       <x:c r="B24" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F24" s="1">
         <x:v>20</x:v>
@@ -7926,16 +7923,16 @@
     <x:row r="25">
       <x:c r="A25" s="1"/>
       <x:c r="B25" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F25" s="1">
         <x:v>20</x:v>
@@ -7947,16 +7944,16 @@
     <x:row r="26">
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F26" s="1">
         <x:v>20</x:v>
@@ -7968,16 +7965,16 @@
     <x:row r="27">
       <x:c r="A27" s="1"/>
       <x:c r="B27" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F27" s="1">
         <x:v>20</x:v>
@@ -7989,16 +7986,16 @@
     <x:row r="28">
       <x:c r="A28" s="1"/>
       <x:c r="B28" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F28" s="1">
         <x:v>20</x:v>
@@ -8010,16 +8007,16 @@
     <x:row r="29">
       <x:c r="A29" s="1"/>
       <x:c r="B29" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F29" s="1">
         <x:v>20</x:v>
@@ -8031,16 +8028,16 @@
     <x:row r="30">
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F30" s="1">
         <x:v>20</x:v>
@@ -8052,16 +8049,16 @@
     <x:row r="31">
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F31" s="1">
         <x:v>20</x:v>
@@ -8073,16 +8070,16 @@
     <x:row r="32">
       <x:c r="A32" s="1"/>
       <x:c r="B32" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F32" s="1">
         <x:v>20</x:v>
@@ -8094,16 +8091,16 @@
     <x:row r="33">
       <x:c r="A33" s="1"/>
       <x:c r="B33" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F33" s="1">
         <x:v>20</x:v>
@@ -8115,16 +8112,16 @@
     <x:row r="34">
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F34" s="1">
         <x:v>20</x:v>
@@ -8136,16 +8133,16 @@
     <x:row r="35">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F35" s="1">
         <x:v>20</x:v>
@@ -8157,16 +8154,16 @@
     <x:row r="36">
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F36" s="1">
         <x:v>20</x:v>
@@ -8178,16 +8175,16 @@
     <x:row r="37">
       <x:c r="A37" s="1"/>
       <x:c r="B37" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F37" s="1">
         <x:v>20</x:v>
@@ -8199,16 +8196,16 @@
     <x:row r="38">
       <x:c r="A38" s="1"/>
       <x:c r="B38" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F38" s="1">
         <x:v>20</x:v>
@@ -8220,16 +8217,16 @@
     <x:row r="39">
       <x:c r="A39" s="1"/>
       <x:c r="B39" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F39" s="1">
         <x:v>20</x:v>
@@ -8241,16 +8238,16 @@
     <x:row r="40">
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F40" s="1">
         <x:v>20</x:v>
@@ -8262,16 +8259,16 @@
     <x:row r="41">
       <x:c r="A41" s="1"/>
       <x:c r="B41" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F41" s="1">
         <x:v>20</x:v>
@@ -8283,16 +8280,16 @@
     <x:row r="42">
       <x:c r="A42" s="1"/>
       <x:c r="B42" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F42" s="1">
         <x:v>10</x:v>
@@ -8304,16 +8301,16 @@
     <x:row r="43">
       <x:c r="A43" s="1"/>
       <x:c r="B43" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F43" s="1">
         <x:v>10</x:v>
@@ -8325,10 +8322,10 @@
     <x:row r="44">
       <x:c r="A44" s="1"/>
       <x:c r="B44" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>3</x:v>
@@ -8346,16 +8343,16 @@
     <x:row r="45">
       <x:c r="A45" s="1"/>
       <x:c r="B45" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F45" s="1">
         <x:v>12</x:v>
@@ -8367,16 +8364,16 @@
     <x:row r="46">
       <x:c r="A46" s="1"/>
       <x:c r="B46" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F46" s="1">
         <x:v>12</x:v>
@@ -8388,10 +8385,10 @@
     <x:row r="47">
       <x:c r="A47" s="1"/>
       <x:c r="B47" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>3</x:v>
@@ -8409,16 +8406,16 @@
     <x:row r="48">
       <x:c r="A48" s="1"/>
       <x:c r="B48" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F48" s="1">
         <x:v>14</x:v>
@@ -8430,16 +8427,16 @@
     <x:row r="49">
       <x:c r="A49" s="1"/>
       <x:c r="B49" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F49" s="1">
         <x:v>14</x:v>
@@ -8451,10 +8448,10 @@
     <x:row r="50">
       <x:c r="A50" s="1"/>
       <x:c r="B50" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>3</x:v>
@@ -8472,16 +8469,16 @@
     <x:row r="51">
       <x:c r="A51" s="1"/>
       <x:c r="B51" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F51" s="1">
         <x:v>16</x:v>
@@ -8493,16 +8490,16 @@
     <x:row r="52">
       <x:c r="A52" s="1"/>
       <x:c r="B52" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F52" s="1">
         <x:v>16</x:v>
@@ -8514,16 +8511,16 @@
     <x:row r="53">
       <x:c r="A53" s="1"/>
       <x:c r="B53" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F53" s="1">
         <x:v>1</x:v>
@@ -8535,16 +8532,16 @@
     <x:row r="54">
       <x:c r="A54" s="1"/>
       <x:c r="B54" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F54" s="1">
         <x:v>18</x:v>
@@ -8556,16 +8553,16 @@
     <x:row r="55">
       <x:c r="A55" s="1"/>
       <x:c r="B55" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F55" s="1">
         <x:v>18</x:v>
@@ -8577,16 +8574,16 @@
     <x:row r="56">
       <x:c r="A56" s="1"/>
       <x:c r="B56" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F56" s="1">
         <x:v>1</x:v>
@@ -8598,16 +8595,16 @@
     <x:row r="57">
       <x:c r="A57" s="1"/>
       <x:c r="B57" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F57" s="1">
         <x:v>20</x:v>
@@ -8619,16 +8616,16 @@
     <x:row r="58">
       <x:c r="A58" s="1"/>
       <x:c r="B58" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F58" s="1">
         <x:v>20</x:v>
@@ -8640,16 +8637,16 @@
     <x:row r="59">
       <x:c r="A59" s="1"/>
       <x:c r="B59" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F59" s="1">
         <x:v>1</x:v>
@@ -8691,31 +8688,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
+      <x:c r="L1" s="2" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
         <x:v>13</x:v>
@@ -8767,37 +8764,37 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C3" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D3" s="4" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="s">
+      <x:c r="F3" s="4" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="s">
+      <x:c r="G3" s="4" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="s">
+      <x:c r="H3" s="4" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="s">
+      <x:c r="I3" s="4" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="s">
+      <x:c r="J3" s="4" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="J3" s="4" t="s">
+      <x:c r="K3" s="4" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="K3" s="4" t="s">
+      <x:c r="L3" s="4" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="L3" s="4" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="M3" s="4" t="s">
         <x:v>35</x:v>
@@ -8806,16 +8803,16 @@
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="E4" s="1" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>256</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>1</x:v>
@@ -8845,16 +8842,16 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>0</x:v>
@@ -8884,16 +8881,16 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>262</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>0</x:v>
@@ -8923,16 +8920,16 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>265</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>0</x:v>
@@ -8965,13 +8962,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>268</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>0</x:v>
@@ -9004,13 +9001,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>271</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>0</x:v>
@@ -9070,58 +9067,58 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="E1" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
+      <x:c r="L1" s="2" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="M1" s="2" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
+      <x:c r="N1" s="2" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="O1" s="2" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="s">
+      <x:c r="P1" s="2" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="s">
+      <x:c r="Q1" s="2" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="Q1" s="2" t="s">
+      <x:c r="R1" s="2" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="R1" s="2" t="s">
+      <x:c r="S1" s="2" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="S1" s="2" t="s">
+      <x:c r="T1" s="2" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="T1" s="2" t="s">
-        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -9191,76 +9188,76 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
+      <x:c r="E3" s="4" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="F3" s="4" t="s">
+      <x:c r="G3" s="4" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="s">
+      <x:c r="H3" s="4" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="I3" s="4" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="I3" s="4" t="s">
+      <x:c r="J3" s="4" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="J3" s="4" t="s">
+      <x:c r="K3" s="4" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="K3" s="4" t="s">
+      <x:c r="L3" s="4" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="L3" s="4" t="s">
+      <x:c r="M3" s="4" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="M3" s="4" t="s">
+      <x:c r="N3" s="4" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="N3" s="4" t="s">
+      <x:c r="O3" s="4" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="O3" s="4" t="s">
+      <x:c r="P3" s="4" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="P3" s="4" t="s">
+      <x:c r="Q3" s="4" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="Q3" s="4" t="s">
+      <x:c r="R3" s="4" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="R3" s="4" t="s">
+      <x:c r="S3" s="4" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="S3" s="4" t="s">
+      <x:c r="T3" s="4" t="s">
         <x:v>303</x:v>
-      </x:c>
-      <x:c r="T3" s="4" t="s">
-        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="E4" s="1" t="s">
         <x:v>307</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>308</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>1</x:v>
@@ -9311,16 +9308,16 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>1</x:v>
@@ -9371,16 +9368,16 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>311</x:v>
-      </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>1</x:v>
@@ -9431,16 +9428,16 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
         <x:v>307</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>308</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>1</x:v>
@@ -9491,13 +9488,13 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>313</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="E8" s="1"/>
       <x:c r="F8" s="1">
@@ -9549,16 +9546,16 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>316</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>1</x:v>
@@ -9609,16 +9606,16 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>316</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>1</x:v>
@@ -9724,133 +9721,133 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="E1" s="2" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="F1" s="2" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
+      <x:c r="L1" s="2" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="M1" s="2" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
+      <x:c r="N1" s="2" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="O1" s="2" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="s">
+      <x:c r="P1" s="2" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="s">
+      <x:c r="Q1" s="2" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="Q1" s="2" t="s">
+      <x:c r="R1" s="2" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="R1" s="2" t="s">
+      <x:c r="S1" s="2" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="S1" s="2" t="s">
+      <x:c r="T1" s="2" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="T1" s="2" t="s">
+      <x:c r="U1" s="2" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="U1" s="2" t="s">
+      <x:c r="V1" s="2" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="V1" s="2" t="s">
-        <x:v>334</x:v>
       </x:c>
       <x:c r="W1" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="X1" s="2" t="s">
-        <x:v>335</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="Y1" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="Z1" s="2" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="AA1" s="2" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="AA1" s="2" t="s">
+      <x:c r="AB1" s="2" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="AB1" s="2" t="s">
+      <x:c r="AC1" s="2" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="AC1" s="2" t="s">
+      <x:c r="AD1" s="2" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="AD1" s="2" t="s">
+      <x:c r="AE1" s="2" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="AE1" s="2" t="s">
+      <x:c r="AF1" s="2" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="AF1" s="2" t="s">
+      <x:c r="AG1" s="2" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="AG1" s="2" t="s">
+      <x:c r="AH1" s="2" t="s">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="AH1" s="2" t="s">
+      <x:c r="AI1" s="2" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="AI1" s="2" t="s">
+      <x:c r="AJ1" s="2" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="AJ1" s="2" t="s">
+      <x:c r="AK1" s="2" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="AK1" s="2" t="s">
+      <x:c r="AL1" s="2" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="AL1" s="2" t="s">
+      <x:c r="AM1" s="2" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="AM1" s="2" t="s">
+      <x:c r="AN1" s="2" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="AN1" s="2" t="s">
+      <x:c r="AO1" s="2" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="AO1" s="2" t="s">
+      <x:c r="AP1" s="2" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="AP1" s="2" t="s">
+      <x:c r="AQ1" s="2" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="AQ1" s="2" t="s">
+      <x:c r="AR1" s="2" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="AR1" s="2" t="s">
+      <x:c r="AS1" s="2" t="s">
         <x:v>354</x:v>
-      </x:c>
-      <x:c r="AS1" s="2" t="s">
-        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -9918,13 +9915,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="V2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="W2" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="X2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="Y2" s="3" t="s">
         <x:v>21</x:v>
@@ -9995,148 +9992,148 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="D3" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E3" s="4" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="s">
+      <x:c r="G3" s="4" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="s">
+      <x:c r="H3" s="4" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="s">
+      <x:c r="I3" s="4" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="J3" s="4" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="K3" s="4" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="J3" s="4" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="K3" s="4" t="s">
+      <x:c r="L3" s="4" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="L3" s="4" t="s">
+      <x:c r="M3" s="4" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="M3" s="4" t="s">
+      <x:c r="N3" s="4" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="N3" s="4" t="s">
+      <x:c r="O3" s="4" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="O3" s="4" t="s">
+      <x:c r="P3" s="4" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="P3" s="4" t="s">
+      <x:c r="Q3" s="4" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="Q3" s="4" t="s">
+      <x:c r="R3" s="4" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="R3" s="4" t="s">
+      <x:c r="S3" s="4" t="s">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="S3" s="4" t="s">
+      <x:c r="T3" s="4" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="T3" s="4" t="s">
+      <x:c r="U3" s="4" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="U3" s="4" t="s">
+      <x:c r="V3" s="4" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="V3" s="4" t="s">
+      <x:c r="W3" s="4" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="W3" s="4" t="s">
+      <x:c r="X3" s="4" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="X3" s="4" t="s">
+      <x:c r="Y3" s="4" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="Z3" s="4" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="Y3" s="4" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="Z3" s="4" t="s">
+      <x:c r="AA3" s="4" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="AA3" s="4" t="s">
+      <x:c r="AB3" s="4" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="AB3" s="4" t="s">
+      <x:c r="AC3" s="4" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="AC3" s="4" t="s">
+      <x:c r="AD3" s="4" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="AD3" s="4" t="s">
+      <x:c r="AE3" s="4" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="AE3" s="4" t="s">
+      <x:c r="AF3" s="4" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="AF3" s="4" t="s">
+      <x:c r="AG3" s="4" t="s">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="AG3" s="4" t="s">
+      <x:c r="AH3" s="4" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="AH3" s="4" t="s">
+      <x:c r="AI3" s="4" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="AI3" s="4" t="s">
+      <x:c r="AJ3" s="4" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="AJ3" s="4" t="s">
+      <x:c r="AK3" s="4" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="AK3" s="4" t="s">
+      <x:c r="AL3" s="4" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="AL3" s="4" t="s">
+      <x:c r="AM3" s="4" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="AM3" s="4" t="s">
+      <x:c r="AN3" s="4" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="AN3" s="4" t="s">
+      <x:c r="AO3" s="4" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="AO3" s="4" t="s">
+      <x:c r="AP3" s="4" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="AP3" s="4" t="s">
+      <x:c r="AQ3" s="4" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="AQ3" s="4" t="s">
+      <x:c r="AR3" s="4" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="AR3" s="4" t="s">
+      <x:c r="AS3" s="4" t="s">
         <x:v>394</x:v>
-      </x:c>
-      <x:c r="AS3" s="4" t="s">
-        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="28">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>1001</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="E4" s="1">
         <x:v>1</x:v>
@@ -10197,18 +10194,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y4" s="1" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Z4" s="1" t="s">
         <x:v>398</x:v>
-      </x:c>
-      <x:c r="Z4" s="1" t="s">
-        <x:v>399</x:v>
       </x:c>
       <x:c r="AA4" s="1"/>
       <x:c r="AB4" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="AC4" s="1"/>
       <x:c r="AD4" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="AE4" s="1"/>
       <x:c r="AF4" s="1"/>
@@ -10239,13 +10236,13 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>1002</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>3</x:v>
@@ -10306,18 +10303,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y5" s="1" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="Z5" s="1" t="s">
         <x:v>404</x:v>
-      </x:c>
-      <x:c r="Z5" s="1" t="s">
-        <x:v>405</x:v>
       </x:c>
       <x:c r="AA5" s="1"/>
       <x:c r="AB5" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="AC5" s="1"/>
       <x:c r="AD5" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="AE5" s="1"/>
       <x:c r="AF5" s="1"/>
@@ -10348,13 +10345,13 @@
     <x:row r="6" ht="28">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>1003</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>5</x:v>
@@ -10415,18 +10412,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y6" s="1" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="Z6" s="1" t="s">
         <x:v>410</x:v>
-      </x:c>
-      <x:c r="Z6" s="1" t="s">
-        <x:v>411</x:v>
       </x:c>
       <x:c r="AA6" s="1"/>
       <x:c r="AB6" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="AC6" s="1"/>
       <x:c r="AD6" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="AE6" s="1"/>
       <x:c r="AF6" s="1"/>
@@ -10457,13 +10454,13 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1004</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>8</x:v>
@@ -10514,7 +10511,7 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="U7" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="V7" s="5" t="b">
         <x:v>0</x:v>
@@ -10529,11 +10526,11 @@
       <x:c r="Z7" s="1"/>
       <x:c r="AA7" s="1"/>
       <x:c r="AB7" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="AC7" s="1"/>
       <x:c r="AD7" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="AE7" s="1"/>
       <x:c r="AF7" s="1"/>
@@ -10564,13 +10561,13 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>1005</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="E8" s="1">
         <x:v>9</x:v>
@@ -10631,18 +10628,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y8" s="1" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="Z8" s="1" t="s">
         <x:v>420</x:v>
-      </x:c>
-      <x:c r="Z8" s="1" t="s">
-        <x:v>421</x:v>
       </x:c>
       <x:c r="AA8" s="1"/>
       <x:c r="AB8" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="AC8" s="1"/>
       <x:c r="AD8" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="AE8" s="1"/>
       <x:c r="AF8" s="1"/>
@@ -10673,13 +10670,13 @@
     <x:row r="9" ht="28">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>1006</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E9" s="1">
         <x:v>1</x:v>
@@ -10743,11 +10740,11 @@
       <x:c r="Z9" s="1"/>
       <x:c r="AA9" s="1"/>
       <x:c r="AB9" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="AC9" s="1"/>
       <x:c r="AD9" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="AE9" s="1"/>
       <x:c r="AF9" s="1"/>
@@ -10778,13 +10775,13 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>1007</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E10" s="1">
         <x:v>1</x:v>
@@ -10845,18 +10842,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y10" s="1" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Z10" s="1" t="s">
         <x:v>398</x:v>
-      </x:c>
-      <x:c r="Z10" s="1" t="s">
-        <x:v>399</x:v>
       </x:c>
       <x:c r="AA10" s="1"/>
       <x:c r="AB10" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="AC10" s="1"/>
       <x:c r="AD10" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="AE10" s="1"/>
       <x:c r="AF10" s="1"/>
@@ -10918,49 +10915,49 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="F1" s="2" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="M1" s="2" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
+      <x:c r="N1" s="2" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="O1" s="2" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="s">
+      <x:c r="P1" s="2" t="s">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="s">
+      <x:c r="Q1" s="2" t="s">
         <x:v>440</x:v>
-      </x:c>
-      <x:c r="Q1" s="2" t="s">
-        <x:v>441</x:v>
       </x:c>
       <x:c r="R1" s="2" t="s">
         <x:v>18</x:v>
@@ -11007,13 +11004,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="O2" s="3" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="s">
         <x:v>20</x:v>
@@ -11027,70 +11024,70 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D3" s="4" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
+      <x:c r="F3" s="4" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="s">
+      <x:c r="G3" s="4" t="s">
         <x:v>445</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="s">
+      <x:c r="H3" s="4" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="s">
+      <x:c r="I3" s="4" t="s">
         <x:v>447</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="s">
+      <x:c r="J3" s="4" t="s">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="J3" s="4" t="s">
+      <x:c r="K3" s="4" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="K3" s="4" t="s">
+      <x:c r="L3" s="4" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L3" s="4" t="s">
+      <x:c r="M3" s="4" t="s">
         <x:v>451</x:v>
       </x:c>
-      <x:c r="M3" s="4" t="s">
+      <x:c r="N3" s="4" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="N3" s="4" t="s">
+      <x:c r="O3" s="4" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="O3" s="4" t="s">
+      <x:c r="P3" s="4" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="P3" s="4" t="s">
+      <x:c r="Q3" s="4" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="Q3" s="4" t="s">
+      <x:c r="R3" s="4" t="s">
         <x:v>456</x:v>
-      </x:c>
-      <x:c r="R3" s="4" t="s">
-        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>0</x:v>
@@ -11135,16 +11132,16 @@
     <x:row r="5">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>0</x:v>
@@ -11189,16 +11186,16 @@
     <x:row r="6">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>0</x:v>
@@ -11243,16 +11240,16 @@
     <x:row r="7">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>0</x:v>
@@ -11297,16 +11294,16 @@
     <x:row r="8">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>0</x:v>
@@ -11351,16 +11348,16 @@
     <x:row r="9">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>463</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>464</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>0</x:v>
@@ -11405,16 +11402,16 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>0</x:v>
@@ -11459,16 +11456,16 @@
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>0</x:v>
@@ -11513,16 +11510,16 @@
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>0</x:v>
@@ -11567,16 +11564,16 @@
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>468</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>469</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>-0.42</x:v>
@@ -11621,16 +11618,16 @@
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>470</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>471</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>0.42</x:v>
@@ -11675,16 +11672,16 @@
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>0</x:v>
@@ -11729,16 +11726,16 @@
     <x:row r="16">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>0</x:v>
@@ -11783,16 +11780,16 @@
     <x:row r="17">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>0</x:v>
@@ -11837,16 +11834,16 @@
     <x:row r="18">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F18" s="1">
         <x:v>0</x:v>
@@ -11891,16 +11888,16 @@
     <x:row r="19">
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
         <x:v>476</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>477</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>0</x:v>
